--- a/data/processed/OSB_Master_Quarterly_Handle_GGR_Hold.xlsx
+++ b/data/processed/OSB_Master_Quarterly_Handle_GGR_Hold.xlsx
@@ -994,7 +994,7 @@
         <v>1659660539.46</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>521196658.12</v>
+        <v>990284027.5599999</v>
       </c>
     </row>
     <row r="5">
@@ -1669,7 +1669,9 @@
       <c r="AI12" s="4" t="n">
         <v>842508713</v>
       </c>
-      <c r="AJ12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n">
+        <v>470602561</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1754,7 +1756,7 @@
         <v>1079150660.16</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>324485986.53</v>
+        <v>642460355.76</v>
       </c>
     </row>
     <row r="14">
@@ -1828,7 +1830,7 @@
         <v>2109589149.42</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>678382514.61</v>
+        <v>1310492193.14</v>
       </c>
     </row>
     <row r="15">
@@ -2122,7 +2124,7 @@
         <v>991499873.15</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>273397862.9</v>
+        <v>529762676.71</v>
       </c>
     </row>
     <row r="19">
@@ -2610,7 +2612,7 @@
         <v>2893156778</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>1847064639</v>
+        <v>2759963926</v>
       </c>
     </row>
     <row r="25">
@@ -2724,7 +2726,7 @@
         <v>3663395869.95</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>922727272.73</v>
+        <v>1878319639.37</v>
       </c>
     </row>
     <row r="26">
@@ -2877,10 +2879,10 @@
         <v>3236939510</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>2358962767</v>
+        <v>1501221414</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>800138386</v>
+        <v>797769455</v>
       </c>
     </row>
     <row r="28">
@@ -2999,10 +3001,10 @@
         <v>12006123.38</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>78447516.69</v>
+        <v>81125657.19</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>95901014.17</v>
+        <v>96713878.54000001</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>362874631.94</v>
@@ -3266,7 +3268,7 @@
         <v>3462257.58</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>596884.16</v>
+        <v>1088021.89</v>
       </c>
     </row>
     <row r="32">
@@ -3358,7 +3360,7 @@
         <v>1554141558</v>
       </c>
       <c r="AJ32" s="4" t="n">
-        <v>923843654</v>
+        <v>1379972912</v>
       </c>
     </row>
     <row r="33">
@@ -3610,7 +3612,7 @@
         <v>122801277.68</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>65955387.66</v>
+        <v>71249229.59999999</v>
       </c>
     </row>
     <row r="36">
@@ -3638,16 +3640,24 @@
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n">
+        <v>6239052.17</v>
+      </c>
       <c r="R36" s="4" t="n">
-        <v>12285011.5</v>
+        <v>34105677.19</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>10301603.38</v>
-      </c>
-      <c r="T36" s="4" t="n"/>
-      <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n"/>
+        <v>36984173.98</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>26659605.68</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>31812429.24</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>49065922.2</v>
+      </c>
       <c r="W36" s="4" t="n">
         <v>40708153.4</v>
       </c>
@@ -3715,10 +3725,10 @@
         <v>1816375511.02</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2865454075.46</v>
+        <v>2868132215.96</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2071677746.49</v>
+        <v>2072490610.86</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>2712441881.82</v>
@@ -3745,22 +3755,22 @@
         <v>11961235304.82</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>12310520243.87</v>
+        <v>12316759296.04</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>23606525995.88</v>
+        <v>23628346661.57</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>28025256311.33</v>
+        <v>28051938881.93</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>19782134946.46</v>
+        <v>19808794552.14</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>17904246444.21</v>
+        <v>17936058873.45</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>29635776182.22</v>
+        <v>29684842104.42</v>
       </c>
       <c r="W37" s="6" t="n">
         <v>32669735329.15</v>
@@ -3799,10 +3809,10 @@
         <v>52879700346.16</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>44784370935.87</v>
+        <v>43926629582.87</v>
       </c>
       <c r="AJ37" s="6" t="n">
-        <v>20664625141.21</v>
+        <v>25138800893.53</v>
       </c>
     </row>
   </sheetData>
@@ -4315,7 +4325,7 @@
         <v>148727838.49</v>
       </c>
       <c r="AJ4" s="4" t="n">
-        <v>49863057.43</v>
+        <v>94516969.84</v>
       </c>
     </row>
     <row r="5">
@@ -4990,7 +5000,9 @@
       <c r="AI12" s="4" t="n">
         <v>85583277</v>
       </c>
-      <c r="AJ12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n">
+        <v>53686441</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5075,7 +5087,7 @@
         <v>143732998.54</v>
       </c>
       <c r="AJ13" s="4" t="n">
-        <v>45844177.7</v>
+        <v>91789336.52</v>
       </c>
     </row>
     <row r="14">
@@ -5149,7 +5161,7 @@
         <v>227478307.39</v>
       </c>
       <c r="AJ14" s="4" t="n">
-        <v>83428332.73999999</v>
+        <v>155554830.83</v>
       </c>
     </row>
     <row r="15">
@@ -5438,10 +5450,10 @@
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n">
-        <v>30157126.48</v>
+        <v>24355000.86</v>
       </c>
       <c r="AJ18" s="4" t="n">
-        <v>32508228.02</v>
+        <v>49641664.13</v>
       </c>
     </row>
     <row r="19">
@@ -5957,7 +5969,7 @@
         <v>261559560</v>
       </c>
       <c r="AJ24" s="4" t="n">
-        <v>182738853</v>
+        <v>265967364</v>
       </c>
     </row>
     <row r="25">
@@ -6071,7 +6083,7 @@
         <v>251327000</v>
       </c>
       <c r="AJ25" s="4" t="n">
-        <v>78680000</v>
+        <v>151389000</v>
       </c>
     </row>
     <row r="26">
@@ -6224,10 +6236,10 @@
         <v>368672628</v>
       </c>
       <c r="AI27" s="4" t="n">
-        <v>226934324</v>
+        <v>154097533</v>
       </c>
       <c r="AJ27" s="4" t="n">
-        <v>89183735</v>
+        <v>88959455</v>
       </c>
     </row>
     <row r="28">
@@ -6346,10 +6358,10 @@
         <v>1450432.15</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7248137.25</v>
+        <v>7355234.2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8329747.89</v>
+        <v>8388274.76</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>34296984.78</v>
@@ -6613,7 +6625,7 @@
         <v>195087.68</v>
       </c>
       <c r="AJ31" s="4" t="n">
-        <v>116694.63</v>
+        <v>132102.37</v>
       </c>
     </row>
     <row r="32">
@@ -6705,7 +6717,7 @@
         <v>155414155.8</v>
       </c>
       <c r="AJ32" s="4" t="n">
-        <v>92384365.40000001</v>
+        <v>137997291.2</v>
       </c>
     </row>
     <row r="33">
@@ -6957,7 +6969,7 @@
         <v>13537442.32</v>
       </c>
       <c r="AJ35" s="4" t="n">
-        <v>8945070.33</v>
+        <v>9734151.380000001</v>
       </c>
     </row>
     <row r="36">
@@ -6985,16 +6997,24 @@
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
+      <c r="Q36" s="4" t="n">
+        <v>955466.4</v>
+      </c>
       <c r="R36" s="4" t="n">
-        <v>813504.21</v>
+        <v>3058400.54</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>722630.77</v>
-      </c>
-      <c r="T36" s="4" t="n"/>
-      <c r="U36" s="4" t="n"/>
-      <c r="V36" s="4" t="n"/>
+        <v>2922326.1</v>
+      </c>
+      <c r="T36" s="4" t="n">
+        <v>2692778.72</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>3851074.09</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>5321051.19</v>
+      </c>
       <c r="W36" s="4" t="n">
         <v>4530826.44</v>
       </c>
@@ -7062,10 +7082,10 @@
         <v>166041365.79</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>164658833.87</v>
+        <v>164765930.82</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>113394310.73</v>
+        <v>113452837.6</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>235375418.82</v>
@@ -7092,22 +7112,22 @@
         <v>936867799.34</v>
       </c>
       <c r="Q37" s="6" t="n">
-        <v>983316267.1799999</v>
+        <v>984271733.58</v>
       </c>
       <c r="R37" s="6" t="n">
-        <v>1564644098.02</v>
+        <v>1566888994.35</v>
       </c>
       <c r="S37" s="6" t="n">
-        <v>1665731013.84</v>
+        <v>1667930709.17</v>
       </c>
       <c r="T37" s="6" t="n">
-        <v>1461726517.91</v>
+        <v>1464419296.63</v>
       </c>
       <c r="U37" s="6" t="n">
-        <v>1848978376.98</v>
+        <v>1852829451.07</v>
       </c>
       <c r="V37" s="6" t="n">
-        <v>2513911436.41</v>
+        <v>2519232487.6</v>
       </c>
       <c r="W37" s="6" t="n">
         <v>2846987019.29</v>
@@ -7146,10 +7166,10 @@
         <v>5465282058.93</v>
       </c>
       <c r="AI37" s="6" t="n">
-        <v>4238270175.34</v>
+        <v>4159631258.72</v>
       </c>
       <c r="AJ37" s="6" t="n">
-        <v>2271870517.52</v>
+        <v>2707546609.54</v>
       </c>
     </row>
   </sheetData>
@@ -7662,7 +7682,7 @@
         <v>0.08961340885913407</v>
       </c>
       <c r="AJ4" s="7" t="n">
-        <v>0.09567033221176095</v>
+        <v>0.09544430406787849</v>
       </c>
     </row>
     <row r="5">
@@ -8337,7 +8357,9 @@
       <c r="AI12" s="7" t="n">
         <v>0.1015814740897522</v>
       </c>
-      <c r="AJ12" s="7" t="n"/>
+      <c r="AJ12" s="7" t="n">
+        <v>0.1140802142808568</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8422,7 +8444,7 @@
         <v>0.133190854480587</v>
       </c>
       <c r="AJ13" s="7" t="n">
-        <v>0.1412824578042649</v>
+        <v>0.1428715961958736</v>
       </c>
     </row>
     <row r="14">
@@ -8496,7 +8518,7 @@
         <v>0.1078306206933903</v>
       </c>
       <c r="AJ14" s="7" t="n">
-        <v>0.12298125459198</v>
+        <v>0.1186995478830617</v>
       </c>
     </row>
     <row r="15">
@@ -8785,10 +8807,10 @@
       <c r="AG18" s="7" t="n"/>
       <c r="AH18" s="7" t="n"/>
       <c r="AI18" s="7" t="n">
-        <v>0.03041566347778811</v>
+        <v>0.02456379624399148</v>
       </c>
       <c r="AJ18" s="7" t="n">
-        <v>0.1189044701197626</v>
+        <v>0.09370547664529902</v>
       </c>
     </row>
     <row r="19">
@@ -9276,7 +9298,7 @@
         <v>0.09040628630599569</v>
       </c>
       <c r="AJ24" s="7" t="n">
-        <v>0.09893473630621544</v>
+        <v>0.09636624649129563</v>
       </c>
     </row>
     <row r="25">
@@ -9390,7 +9412,7 @@
         <v>0.06860492529938629</v>
       </c>
       <c r="AJ25" s="7" t="n">
-        <v>0.08526896551698936</v>
+        <v>0.08059810312731266</v>
       </c>
     </row>
     <row r="26">
@@ -9543,10 +9565,10 @@
         <v>0.1138954332822858</v>
       </c>
       <c r="AI27" s="7" t="n">
-        <v>0.09620089268666274</v>
+        <v>0.1026481047785</v>
       </c>
       <c r="AJ27" s="7" t="n">
-        <v>0.1114603880534236</v>
+        <v>0.1115102294810222</v>
       </c>
     </row>
     <row r="28">
@@ -9665,10 +9687,10 @@
         <v>0.120807699878893</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0.09239473160944491</v>
+        <v>0.09066471021336327</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0.08685776643857154</v>
+        <v>0.08673289590522093</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.09451469394992286</v>
@@ -9932,7 +9954,7 @@
         <v>0.05634695729368581</v>
       </c>
       <c r="AJ31" s="7" t="n">
-        <v>0.1955063273919013</v>
+        <v>0.1214151766744325</v>
       </c>
     </row>
     <row r="32">
@@ -10276,7 +10298,7 @@
         <v>0.1102386113219144</v>
       </c>
       <c r="AJ35" s="7" t="n">
-        <v>0.1356230422920389</v>
+        <v>0.1366211457253427</v>
       </c>
     </row>
     <row r="36">
@@ -10304,16 +10326,24 @@
       <c r="N36" s="7" t="n"/>
       <c r="O36" s="7" t="n"/>
       <c r="P36" s="7" t="n"/>
-      <c r="Q36" s="7" t="n"/>
+      <c r="Q36" s="7" t="n">
+        <v>0.1531428771495591</v>
+      </c>
       <c r="R36" s="7" t="n">
-        <v>0.06621924692540988</v>
+        <v>0.08967423584530795</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>0.0701474074805625</v>
-      </c>
-      <c r="T36" s="7" t="n"/>
-      <c r="U36" s="7" t="n"/>
-      <c r="V36" s="7" t="n"/>
+        <v>0.07901558384351944</v>
+      </c>
+      <c r="T36" s="7" t="n">
+        <v>0.1010059470617046</v>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>0.1210556434073816</v>
+      </c>
+      <c r="V36" s="7" t="n">
+        <v>0.1084469821704482</v>
+      </c>
       <c r="W36" s="7" t="n">
         <v>0.1113002202649654</v>
       </c>
@@ -10381,10 +10411,10 @@
         <v>0.0914135677246376</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>0.05746343495090454</v>
+        <v>0.05744711833824954</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.05473549683203461</v>
+        <v>0.05474226855624772</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>0.08677620722404836</v>
@@ -10411,22 +10441,22 @@
         <v>0.07832533809969208</v>
       </c>
       <c r="Q37" s="8" t="n">
-        <v>0.0798760935931721</v>
+        <v>0.07991320686898999</v>
       </c>
       <c r="R37" s="8" t="n">
-        <v>0.066280150594504</v>
+        <v>0.06631394979905408</v>
       </c>
       <c r="S37" s="8" t="n">
-        <v>0.05943678071435091</v>
+        <v>0.05945866045802695</v>
       </c>
       <c r="T37" s="8" t="n">
-        <v>0.07389124186373904</v>
+        <v>0.07392773410695981</v>
       </c>
       <c r="U37" s="8" t="n">
-        <v>0.1032703824057301</v>
+        <v>0.103301927371161</v>
       </c>
       <c r="V37" s="8" t="n">
-        <v>0.08482691396212604</v>
+        <v>0.08486595545087613</v>
       </c>
       <c r="W37" s="8" t="n">
         <v>0.08714447762145591</v>
@@ -10465,10 +10495,10 @@
         <v>0.1033531208224193</v>
       </c>
       <c r="AI37" s="8" t="n">
-        <v>0.09463726042750689</v>
+        <v>0.0946949788367584</v>
       </c>
       <c r="AJ37" s="8" t="n">
-        <v>0.1099400788543398</v>
+        <v>0.1077038885429434</v>
       </c>
     </row>
   </sheetData>
@@ -10506,7 +10536,7 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:56 UTC</t>
+          <t>2026-07-08 17:37 UTC</t>
         </is>
       </c>
     </row>
